--- a/AAII_Financials/Quarterly/EQT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EQT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>EQT</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1727800</v>
+      </c>
+      <c r="E8" s="3">
         <v>3555500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2228000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1782600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1798000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2372100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1756100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1177300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>850300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1258200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1337200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>985400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>834900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1816700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3479800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2069500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2527500</v>
       </c>
-      <c r="T8" s="3" t="s">
+      <c r="U8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3839700</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="3">
         <v>949900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1252600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>172100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>527100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1107100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1011500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>951600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1310300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1143200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>910700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1050000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>950600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1312000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>848700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>659400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>688700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>897500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>379000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>556700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>447900</v>
+      </c>
+      <c r="E9" s="3">
         <v>454100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>452100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>435200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>440900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>420000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>438300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>495000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>590700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>588300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>605400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>594900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>558700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>543400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>585700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>622900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>622300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>587100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>610100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>552700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>511600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>493000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>474600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>467400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>444000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>480200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>474800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>475800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>473300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>482700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1166700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>493400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>501200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>501000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>839300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>195300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>197400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>199800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>184700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>147100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3101500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1775800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1347400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1357100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1952100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1317800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>682300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>259600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>669900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>731800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>390600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>276200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1273300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2894100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1446600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1905200</v>
       </c>
-      <c r="T10" s="3" t="s">
+      <c r="U10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3229600</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="3">
         <v>456900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>778000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-295300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>83100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>626900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>536700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>475800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>837000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>660500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-256000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>556600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>449400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>811000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>9400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>464100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>491300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>697700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>194300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>409600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1279,38 +1293,38 @@
       <c r="P12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>20500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3200</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>900</v>
       </c>
       <c r="AB12" s="3">
         <v>900</v>
@@ -1319,46 +1333,49 @@
         <v>900</v>
       </c>
       <c r="AD12" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE12" s="3">
         <v>3500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>-35300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>3600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>8500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>2400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>3500</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>3100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>4000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E14" s="3">
         <v>33300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>212200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>20800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>12100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-326400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>297600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-299600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>152500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>20500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>121700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>48000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>150400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>220700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>242300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>79500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>19400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>29400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>220600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>60700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>95600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>119200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1567700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>155700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>70100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>33600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>747200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>311800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>168700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2343000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>157300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>10800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>4200</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>58700</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>689600</v>
+      </c>
+      <c r="E15" s="3">
         <v>654800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>667800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>688400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>623500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>620800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>620300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>589300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>466000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>486800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>501900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>446900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>395700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>387700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>396000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>418700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>429100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>422100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>476400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>442900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>380300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>377100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>375400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>348500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>330600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>365000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>391700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>398700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>382800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>401500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>278200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>398400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>382100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>403000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>257100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>246600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>240800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>231900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>245000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>237100</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1515800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1002800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1160500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>657700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1873000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1363800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1162000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1129800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1066200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>462100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>961700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>864800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>178800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1161000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1172700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1270000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1316100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1382300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1144700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>962900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>945500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1111200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>936100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>914300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1000300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2473600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1113100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1014200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>967700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2142100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1197500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1065300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3262400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1198300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>521400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>498600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>506900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>568500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>448300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>403800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2039800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1225200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>622100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1140300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>499100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>392400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-279500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>192100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>875100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-29900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1638000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2318800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>896800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1257500</v>
       </c>
-      <c r="T18" s="3" t="s">
+      <c r="U18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2457400</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y18" s="3">
         <v>4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>141400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-764000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-387200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>106800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1462100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-161500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>296100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>175500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1231400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-147500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-114700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1950400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-349600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>138000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>190100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>390600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-189500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>108400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>10900</v>
       </c>
-      <c r="T20" s="3" t="s">
+      <c r="U20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12700</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y20" s="3">
         <v>15200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>6700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>86500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-178700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-36300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-238200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-81100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>110000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-97300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4400</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ20" s="3">
         <v>-100</v>
       </c>
       <c r="AK20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-18900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>6500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>6300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>3400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>8500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1096800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2694700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1894000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1310900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1766400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1120500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1015100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>608600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>186900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>679000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1377300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>470800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>366400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2025800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2724500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1318500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1697600</v>
       </c>
-      <c r="T21" s="3" t="s">
+      <c r="U21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2946500</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="3">
         <v>396700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>510400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-408700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>29900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>293100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1106700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>597700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>687000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-874700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>312900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>323600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-1491800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>391100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>437200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>625900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>64000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>356300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E22" s="3">
         <v>96800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>105500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>109900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>105700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>117600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>186400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>158300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>55700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>54400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>72800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>60400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>46500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>55600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>60100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>66000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>67900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>71500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>75500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>72300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>70500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>74300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>69200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>65400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>62400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>45100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>47700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>50500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>56600</v>
       </c>
-      <c r="AG22" s="3" t="s">
+      <c r="AH22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>56200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>57100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>57900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>30900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>50400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>44100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>42700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>39500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>366400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1987300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>954700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>536500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1092300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>394100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>574100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-402300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>127400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>652400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-46100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-78700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1575900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2272800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>839700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1202500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1980300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2398600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2637600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1279600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-50900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>60800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-826400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-366100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-134300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1543500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-447400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>164400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>228900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1328700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-199300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-171900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2008400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-399300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>94200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>152400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>351400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-220400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>83200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E24" s="3">
         <v>433400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>208300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>129300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>235600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>78700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>146900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-104900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-44200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>151000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-126900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>356600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>559000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>152200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>308200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-465700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>592600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-661400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-346300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-225800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-103000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>32800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-366500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-86300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>38900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>38200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-198300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-72000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-94900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-429800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-102400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-11300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>29700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>100700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-111600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>281400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1553900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>746400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>407200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>856700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>315400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>427200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-297400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>103100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>501400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>80700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-66900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1219200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1713800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>687500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>894200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1514600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1806000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1976200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-933300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-37900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>63700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-263100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-167100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1176900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-361000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>125600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>190700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1130400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-127300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-77000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1578500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-296900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>105500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>122600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>250700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-108800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>70100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1487200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>677100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>335900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>784100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>242100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>418400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>103500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>502100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>81300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-66600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1218500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1712000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>683700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>891400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1516000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1804800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1976800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-933300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>63700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-263100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-167100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1176900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-361000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>125600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>190700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1005200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-230500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-195500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1719500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-396200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>23300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>41100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>164000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-192000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,14 +3285,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3243,22 +3304,22 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>368500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>190800</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>213300</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>133600</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>1676300</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3266,14 +3327,17 @@
       <c r="AN29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-10900</v>
       </c>
-      <c r="T32" s="3" t="s">
+      <c r="U32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12700</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-86500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>178700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>36300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>238200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>81100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-110000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>97300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>100</v>
       </c>
       <c r="AJ32" s="3">
         <v>100</v>
       </c>
       <c r="AK32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL32" s="3">
         <v>18900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-6500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1487200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>677100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>335900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>784100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>242100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>418400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>103500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>502100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>81300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-66600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1218500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1712000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>683700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>891400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1516000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1804800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1976800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-933300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>63700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-263100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-167100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1176900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-361000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>125600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>190700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-636700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-39700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1586000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1280100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>23300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>41100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>164000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-192000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1487200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>677100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>335900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>784100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>242100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>418400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>103500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>502100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>81300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-66600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1218500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1712000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>683700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>891400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1516000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1804800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1976800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-933300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>63700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-263100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-167100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1176900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-361000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>125600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>190700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-636700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-39700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1586000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1280100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>23300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>41100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>164000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-192000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>112900</v>
+      </c>
+      <c r="E41" s="3">
         <v>326600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>110800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>235700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>555500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>281800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>202100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>648000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>81000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1215500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2127300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1458600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>87500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>114000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>330800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>40700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>18200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>18700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>30200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>40800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>698000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>210400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>147300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>483600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>572300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>899400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1103500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1757400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4458,135 +4548,141 @@
         <v>0</v>
       </c>
       <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
         <v>286400</v>
       </c>
-      <c r="AP42" s="3" t="s">
+      <c r="AQ42" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>835100</v>
+      </c>
+      <c r="E43" s="3">
         <v>953300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1485700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>803900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>817400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1298500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1230000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>670400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>676700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>535800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>915100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>559300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>475200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>628100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1608100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1938700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2059000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1212600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2876100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1132400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>651600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>682500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>566600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>479200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>543400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>832800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>908900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>680000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>766400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>948100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1373400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>882400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>774700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>674100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>725200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>279200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>311000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>279000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>341600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>189400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,287 +4803,296 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>138900</v>
+      </c>
+      <c r="E45" s="3">
         <v>184000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>239200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>123600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>118900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>66400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>230600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>251700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>424400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>818000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>991700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>592500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>683600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>978400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>947700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1876200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1982900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1796400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>734800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2185700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1186300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>590500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>630700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>849300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>995400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1096600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>841300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>807600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>801500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>391100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>592800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>347400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>308100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>307100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>290500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>95700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>113500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>73600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>96700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>199200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1177800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1556700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1895200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1267000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1631300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1739100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1714700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1082300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1229800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2095800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2013000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1247200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2425600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3949600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4014400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3902500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4085600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3025900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2286800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3340900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2168700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1313700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1215500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1342200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1541800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1948000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1754900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1495200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1598100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1380000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1969700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1234700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1780800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1191600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1163100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>858500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>996900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1252000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1828200</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2146100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3946500</v>
+      </c>
+      <c r="E47" s="3">
         <v>3915600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3630600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3600500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3623200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3580000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3617400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3358300</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N47" s="3">
         <v>92700</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>10</v>
@@ -4995,11 +5100,11 @@
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R47" s="3">
-        <v>29300</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
         <v>29300</v>
@@ -5008,7 +5113,7 @@
         <v>29300</v>
       </c>
       <c r="U47" s="3">
-        <v>410000</v>
+        <v>29300</v>
       </c>
       <c r="V47" s="3">
         <v>410000</v>
@@ -5017,222 +5122,228 @@
         <v>410000</v>
       </c>
       <c r="X47" s="3">
+        <v>410000</v>
+      </c>
+      <c r="Y47" s="3">
         <v>390000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>613400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>539900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>565700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>510500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>676000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>736200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>997300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1102100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1013000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1300400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1003300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>546400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>460500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>340000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>260700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>237300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>184600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>160300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33552600</v>
+      </c>
+      <c r="E48" s="3">
         <v>33528500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33667600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33610000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31624200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31660700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31843100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32546500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23176300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23022600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22999000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22922100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18323500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18233700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18167300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18132200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18202100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18295900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18445000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18781100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15819100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>15898000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16075900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>15557400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>15704100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15965500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16207700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17629100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17557300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17520500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17392500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>23129900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>23164700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>22875800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>24885000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>14541300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>14257300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>13950100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>13162200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>12407800</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2255600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2259300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2262900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2266600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2270300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2278100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2294700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2446500</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>22600</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
@@ -5263,47 +5374,47 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-      <c r="Y49" s="3" t="s">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>18500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>26000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>33500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>56600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>67000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>77300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2672900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2693600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2714400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2735100</v>
-      </c>
-      <c r="AL49" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM49" s="3" t="s">
         <v>10</v>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ49" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>388400</v>
+      </c>
+      <c r="E52" s="3">
         <v>432100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>336600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>451100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>517700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>445400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>360300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>511900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>320000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>157900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>385700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>524400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>507200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>488200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>477200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>304700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>463500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>465600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>479700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>587500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>437700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>208800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>131700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>186200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>191900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>144700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>266400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>270000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>270100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>268800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>323400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>320800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>304100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>278900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>245000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>209200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>207200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>297900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>175800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41320800</v>
+      </c>
+      <c r="E54" s="3">
         <v>41692300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>41792900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41195300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39666700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39703400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>39830300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39945600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24706500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25438300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25285100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24555000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21273500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22690500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22669900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22541100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22621700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21814600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21607400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23011700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18985300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18039400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18113500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17574700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18008900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18634500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18809200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20160400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20479300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20339700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>20721300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28661300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>28963200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>27632300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>29522600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15984600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>15724000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>15646600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15472900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>14890000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1167000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1414900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1367400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1120000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1151700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1336700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1177700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1042400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1198200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1124900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1272500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1159700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1049900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1153300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1574600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1678100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1416300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1339300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1183200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>820100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>812300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>705500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>693100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>686500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>692300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>796400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>755100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>850800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>877500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1059900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>978800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>754100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>699500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>654600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>388100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>368400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>318100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>310000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>264800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E58" s="3">
         <v>507500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>565200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>506700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>391800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>285000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>362700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>607000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>338800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>414600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>413900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>413200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>422600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>422000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>440900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>493800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1061000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>399700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>29300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>154200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>33400</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>16300</v>
       </c>
       <c r="AB58" s="3">
         <v>16300</v>
       </c>
       <c r="AC58" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AD58" s="3">
         <v>16200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>704700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>704400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>699500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>699300</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
-      </c>
       <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
         <v>8000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>707500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>707200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>207900</v>
       </c>
-      <c r="AO58" s="3">
-        <v>0</v>
-      </c>
       <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>364600</v>
+      </c>
+      <c r="E59" s="3">
         <v>355700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>174400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>429500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>619900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>514400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>481400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>481000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>641700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>232500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>544600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>719000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1097900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1735000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4537800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5048400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5695200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2786000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6032700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2459400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>908500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>902800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1113000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>857800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>764700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>533300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>689700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>677600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>603300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>590700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>967800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>902800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>409200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>569600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>339700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>280100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>368700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>494700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>262800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1750300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2365800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2484800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2191400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2306400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3062300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2461500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2114000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1685600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2373600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2036800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2118900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2182800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2664400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3732200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6637900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7189700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7605300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5186200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7228400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3679200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1750000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1762400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1839500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1560600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1473200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1345900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1449700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1533300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2185500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2355000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2646100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2356200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1108700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1232200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1435300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1355700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>894700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>804600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>618600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5540800</v>
+      </c>
+      <c r="E61" s="3">
         <v>5484900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7350600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7711100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7923200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8107800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9062000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13393400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4945400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4897800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5514900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5501300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4257600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5058600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5256300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4347300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4601200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4556500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4530100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6177200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5096600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4776800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4771300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4697600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4604000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5020600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5276800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5154500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4993000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4343400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4793000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7808600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7833600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7456800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7323600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2691000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2585000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3082900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3289500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2796800</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1202400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1172300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1125300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1237300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1216300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1243700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1177400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1203600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1068500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1067300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1047700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>973800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>910400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>933600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2468000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1897300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1740700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1446800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1920000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1346500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1907000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2282300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2317000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2191800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2405400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2506800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2383000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2658600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2704600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2671200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2615100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1989300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2070800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2203100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2552200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2433700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2405700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2358400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2259600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2200300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12457400</v>
+      </c>
+      <c r="E66" s="3">
         <v>12905200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14432700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14405000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14568900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15300100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15552100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19457300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9581700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10266900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10504300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10345400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9228400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10536900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11497500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12922200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13560500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13625900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11652600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14763300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10693500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8819800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8858200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8728900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8570000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9000600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9005600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9262800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9230900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9200100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9763100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17661200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17283900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>15916000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>16203000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9897000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>9661800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>9627300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>9612600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>8843800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5731300</v>
+      </c>
+      <c r="E72" s="3">
         <v>5623100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4237100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3663100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3425700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2736000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2585200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2261100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2655900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2716000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2681900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2245600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2217700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2338600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1283600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-299600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-880100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1725300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-94400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1908800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>71300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1007700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1048300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>984600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1585200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1848300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2023100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3117000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3485700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3367800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3184300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2369300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2416800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2407000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3996800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2721900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2703800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2667900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2509100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2706200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25258900</v>
+      </c>
+      <c r="E76" s="3">
         <v>25118800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23752700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23151600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21423300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20717900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20597600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20334800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15117800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15164200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14773200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14201300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12005800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12112100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11172500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9619000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9061200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8188700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9954800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8248500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8291800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9219600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9255200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8845800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9438800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9633900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9803600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10897600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11248500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11139600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10958200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11000200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11679300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11716300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13319600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6087700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6062200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6019300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5860300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6046200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1487200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>677100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>335900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>784100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>242100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>418400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>103500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>502100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>81300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-66600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1218500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1712000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>683700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>891400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1516000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1804800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1976800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-933300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>63700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-263100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-167100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1176900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-361000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>125600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>190700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-636700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-39700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1586000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1280100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>23300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>41100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>164000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-192000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>620100</v>
+      </c>
+      <c r="E83" s="3">
         <v>617400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>617600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>586100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>466000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>486800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>501900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>438900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>395700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>387700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>396000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>418700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>429100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>422100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>396000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>418700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>429100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>422100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>476400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>442900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>380300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>377100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>375400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>348500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>330600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>365000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>391700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>398700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>382800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>401500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>454100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>456000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>438400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>458600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>369200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>246600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>240800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>231900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>245000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>237100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3055000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1125400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1017700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1241700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1741200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>756300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>593000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>322000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1155700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>624400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>454600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>437100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1662800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1063800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1150100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>230400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1021200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1170900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>43500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>399900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>406100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>184500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>446900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>500300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>217900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>319000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>443500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>871300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>530900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>904300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>636700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>904400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>426300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>402400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>294200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>514800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>296600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>274300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-650200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-598500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-612700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-626400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-543200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-549600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-499600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-591600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-569500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-558200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-534500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-533100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-504100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-487000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-494800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-353000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-362500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-392700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-292300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-348200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-236700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-219000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-251300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-253800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-276300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-255900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-256200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-345100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-491600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-394800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-371000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>2191600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-915200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-751700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-558700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>1141400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-472400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-369100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-311400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-346200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-371600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-681100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-842400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-621000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1025900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-664000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-534000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>582400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1283100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-312100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-567200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-539500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2790300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-485500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-498300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-404600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-509500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-216500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-291200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-357900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-427000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-247900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-933100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-273700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-145300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-203700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-344900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-491600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-394300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-370300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1259600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-957200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-912800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-849400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2410600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-523700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-551000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-641900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1292000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-809600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,65 +10455,66 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E96" s="3">
         <v>103100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>103000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>98300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>94300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>94100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>94000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>93600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>69600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>69400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>65800</v>
-      </c>
-      <c r="N96" s="3">
-        <v>54200</v>
       </c>
       <c r="O96" s="3">
         <v>54200</v>
       </c>
       <c r="P96" s="3">
+        <v>54200</v>
+      </c>
+      <c r="Q96" s="3">
         <v>54100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-54900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-55500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-46200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-47100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -10300,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
-        <v>-7700</v>
+        <v>0</v>
       </c>
       <c r="AC96" s="3">
         <v>-7700</v>
@@ -10315,19 +10549,19 @@
         <v>-7700</v>
       </c>
       <c r="AG96" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-7900</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-5200</v>
       </c>
       <c r="AL96" s="3">
         <v>-5200</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>-5200</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-5200</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-580600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1996800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-629300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-311600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-304000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1127500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1225500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>749100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-628100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-68600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1185000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-863400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-495800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>711900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-596900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>12900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-827100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-721900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>683900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>673600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-129500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>531500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-317300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-282500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>124100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>149900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-463600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>727400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-640200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>763700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>8100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1648000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>32500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-70200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-77100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>341600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-213700</v>
+      </c>
+      <c r="E102" s="3">
         <v>215800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-124900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-319800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>273700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>79700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>113100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>59000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-618100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>567100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1150700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-911800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>668600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1371100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>43800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>26800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-97100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>91200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-308000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>290100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-22600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>37400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-693200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>487700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>63100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-336200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-88800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-327000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-204200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-653900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-499600</v>
       </c>
     </row>
